--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4NXFR1610K1XQKE38YN99F</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Features</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01KJ4VFN33XPZS3QWAKP8W5K9Q</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4VFN33XPZS3QWAKP8W5K9Q</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,292 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01KJ4WHTS4248FWPK88KT3A7BM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WHTS4248FWPK88KT3A7BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KJ4WHTS55BASXQA1R2SA1E1Z</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WHTS55BASXQA1R2SA1E1Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KJ4WKVQZSBDC5G5QC911Z1C5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WKVQZSBDC5G5QC911Z1C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KJ4WKVR0EXH6RDEXDBZ3G4HX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WKVR0EXH6RDEXDBZ3G4HX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KJ4WRMEYK72N2SRR8QV6YE5S</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WRMEYK72N2SRR8QV6YE5S</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Features</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KJ4X0ZWSCZBR90HPAWRAJZDQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4X0ZWSCZBR90HPAWRAJZDQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KJ4XTQZNGBTEEAFST0DTKVZ0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4XTQZNGBTEEAFST0DTKVZ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Workforce Now Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KJ4Y4X3TVTPSCK1WBK8EQN5W</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4Y4X3TVTPSCK1WBK8EQN5W</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KJ4YW0P6RR32Q0TXW5BQD57Y</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4YW0P6RR32Q0TXW5BQD57Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Onboarding and Offboarding Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KJ4ZQMWG40CFJSM7D7ZKWKEN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4ZQMWG40CFJSM7D7ZKWKEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Onboarding Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KJ502A8K5BNTCFPJ610JDD85</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ502A8K5BNTCFPJ610JDD85</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Offboarding Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KJ4ZQMWJR5RR7EV1Y243W131</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4ZQMWJR5RR7EV1Y243W131</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,50 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KJ9HTG01DFXT0T0BFF2EE75D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9HTG01DFXT0T0BFF2EE75D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KJ9MM4XRY2JMEWK806KPJ1GW</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9MM4XRY2JMEWK806KPJ1GW</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,160 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KJ9QM8WFATC3M86GGED4EJK7</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9QM8WFATC3M86GGED4EJK7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KJ9RF8TAGGXZ3MY0KHEHM58H</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RF8TAGGXZ3MY0KHEHM58H</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Success Notifications</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KJ9RHTP9GP4NW1AJ53H5PR1Y</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RHTP9GP4NW1AJ53H5PR1Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Failure Notifications</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KJ9RJSEP72NRB3DVT3XPFMPW</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RJSEP72NRB3DVT3XPFMPW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KJ9RRGG7600CDTXQNXDK94NJ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RRGG7600CDTXQNXDK94NJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KJ9S3ZCCSJV72TA40YZ02EF6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9S3ZCCSJV72TA40YZ02EF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KJ9SF234ZRXAKS3SXAQAKSV3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9SF234ZRXAKS3SXAQAKSV3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01KJ4NXFR1610K1XQKE38YN99F</t>
+          <t>h_01KJBZQEYXSCQRGE1N2ZDCBAQR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4NXFR1610K1XQKE38YN99F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZQEYXSCQRGE1N2ZDCBAQR</t>
         </is>
       </c>
     </row>
@@ -473,12 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KJ4VFN33XPZS3QWAKP8W5K9Q</t>
+          <t>h_01KJBZQM4GNW8CQ2R32RYCJM6E</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4VFN33XPZS3QWAKP8W5K9Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZQM4GNW8CQ2R32RYCJM6E</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>h_01KJBZQTW7VQA0KBWMA7YP3XGF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZQTW7VQA0KBWMA7YP3XGF</t>
         </is>
       </c>
     </row>
@@ -512,24 +512,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KJ4WHTS4248FWPK88KT3A7BM</t>
+          <t>h_01KJBZR2N6GDQY737FJ0K7QC43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WHTS4248FWPK88KT3A7BM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZR2N6GDQY737FJ0K7QC43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,261 +539,261 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KJ4WHTS55BASXQA1R2SA1E1Z</t>
+          <t>h_01KJBZRBX8PFVCXE0XMZN23ZF9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WHTS55BASXQA1R2SA1E1Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZRBX8PFVCXE0XMZN23ZF9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KJ4WKVQZSBDC5G5QC911Z1C5</t>
+          <t>h_01KJBZRM52QJ26HN0CP93KFXB2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WKVQZSBDC5G5QC911Z1C5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZRM52QJ26HN0CP93KFXB2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KJ4WKVR0EXH6RDEXDBZ3G4HX</t>
+          <t>h_01KJBZRXFW0SBQGZYTSWP1GPBA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WKVR0EXH6RDEXDBZ3G4HX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZRXFW0SBQGZYTSWP1GPBA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KJ4WRMEYK72N2SRR8QV6YE5S</t>
+          <t>h_01KJBZS539HEZKQEC2QKG6XJ50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4WRMEYK72N2SRR8QV6YE5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZS539HEZKQEC2QKG6XJ50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KJ4X0ZWSCZBR90HPAWRAJZDQ</t>
+          <t>h_01KJBZSD23Z4RZW32GZZZ6BM55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4X0ZWSCZBR90HPAWRAJZDQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZSD23Z4RZW32GZZZ6BM55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Workforce Now Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KJ4XTQZNGBTEEAFST0DTKVZ0</t>
+          <t>h_01KJBZSJJDETBM15H2HE780Y5H</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4XTQZNGBTEEAFST0DTKVZ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZSJJDETBM15H2HE780Y5H</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Workforce Now Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KJ4Y4X3TVTPSCK1WBK8EQN5W</t>
+          <t>h_01KJBZTGEW1XXREXCN26ECYRM1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4Y4X3TVTPSCK1WBK8EQN5W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZTGEW1XXREXCN26ECYRM1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Onboarding and Offboarding Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJ4YW0P6RR32Q0TXW5BQD57Y</t>
+          <t>h_01KJBZV4H65SE38XQVE77VWWRN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4YW0P6RR32Q0TXW5BQD57Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZV4H65SE38XQVE77VWWRN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Onboarding and Offboarding Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJ4ZQMWG40CFJSM7D7ZKWKEN</t>
+          <t>h_01KJBZWMHN3CT02DR7CY0TYHS1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4ZQMWG40CFJSM7D7ZKWKEN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZWMHN3CT02DR7CY0TYHS1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Onboarding Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJ502A8K5BNTCFPJ610JDD85</t>
+          <t>h_01KJBZXKQVBA7MT6TF4FN456B4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ502A8K5BNTCFPJ610JDD85</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZXKQVBA7MT6TF4FN456B4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Offboarding Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJ4ZQMWJR5RR7EV1Y243W131</t>
+          <t>h_01KJBZY96JKQRDNK0AY2J2A47S</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ4ZQMWJR5RR7EV1Y243W131</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZY96JKQRDNK0AY2J2A47S</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJ9HTG01DFXT0T0BFF2EE75D</t>
+          <t>h_01KJBZYQ7STWG3WSMB3GX649KY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9HTG01DFXT0T0BFF2EE75D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZYQ7STWG3WSMB3GX649KY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,166 +803,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJ9MM4XRY2JMEWK806KPJ1GW</t>
+          <t>h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9MM4XRY2JMEWK806KPJ1GW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJ9QM8WFATC3M86GGED4EJK7</t>
+          <t>h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9QM8WFATC3M86GGED4EJK7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Notification Settings</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>h_01KJ9RF8TAGGXZ3MY0KHEHM58H</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RF8TAGGXZ3MY0KHEHM58H</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Success Notifications</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>h_01KJ9RHTP9GP4NW1AJ53H5PR1Y</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RHTP9GP4NW1AJ53H5PR1Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Failure Notifications</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>h_01KJ9RJSEP72NRB3DVT3XPFMPW</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RJSEP72NRB3DVT3XPFMPW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Notification Report Settings</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h_01KJ9RRGG7600CDTXQNXDK94NJ</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9RRGG7600CDTXQNXDK94NJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Log Insights Settings</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01KJ9S3ZCCSJV72TA40YZ02EF6</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9S3ZCCSJV72TA40YZ02EF6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Attribute Map</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01KJ9SF234ZRXAKS3SXAQAKSV3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJ9SF234ZRXAKS3SXAQAKSV3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Workforce Now Settings</t>
+          <t>Worker Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Onboarding and Offboarding Settings</t>
+          <t>Date Offset</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJBZV4H65SE38XQVE77VWWRN</t>
+          <t>h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZV4H65SE38XQVE77VWWRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Onboarding Date Offset</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJBZWMHN3CT02DR7CY0TYHS1</t>
+          <t>h_01KHKANS7965H6AX88QT0E48QG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZWMHN3CT02DR7CY0TYHS1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KHKANS7965H6AX88QT0E48QG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Offboarding Date Offset</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJBZXKQVBA7MT6TF4FN456B4</t>
+          <t>h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZXKQVBA7MT6TF4FN456B4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJBZY96JKQRDNK0AY2J2A47S</t>
+          <t>h_01KJBZWMHN3CT02DR7CY0TYHS1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZY96JKQRDNK0AY2J2A47S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZWMHN3CT02DR7CY0TYHS1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJBZYQ7STWG3WSMB3GX649KY</t>
+          <t>h_01KJBZXKQVBA7MT6TF4FN456B4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZYQ7STWG3WSMB3GX649KY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZXKQVBA7MT6TF4FN456B4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,34 +803,210 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+          <t>h_01KJBZY96JKQRDNK0AY2J2A47S</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZY96JKQRDNK0AY2J2A47S</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KJBZYQ7STWG3WSMB3GX649KY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZYQ7STWG3WSMB3GX649KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Attribute Map</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJBZZQGVD2CX5G52BN7Z2W0F</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADP Workforce Now Worker Group Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KJC0Z0ZJR8SF88MCP04YE08M</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJC0Z0ZJR8SF88MCP04YE08M</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Using Different Attribute</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KJC1DVZQSGB6PK97FXYT910X</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KJC1DVZQSGB6PK97FXYT910X</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-Microsoft-Entra-ID-User-Provisioning-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>
